--- a/data/OP2/case18_2_10/case18_operational_data.xlsx
+++ b/data/OP2/case18_2_10/case18_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case18_2_10/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706ADA40-D57B-C445-ABB9-EB0025ABE21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1776B9-AF3F-0846-9733-43342641797A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -454,8 +454,8 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*3.5</f>
-        <v>0.70000000000000007</v>
+        <f>E2*3</f>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C2" s="1">
         <f>F2*-1.5</f>
@@ -477,8 +477,8 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B31" si="0">E3*3.5</f>
-        <v>1.4000000000000001</v>
+        <f t="shared" ref="B3:B31" si="0">E3*3</f>
+        <v>1.2000000000000002</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:C31" si="1">F3*-1.5</f>
@@ -501,7 +501,7 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
@@ -509,7 +509,7 @@
       </c>
       <c r="D4" s="2">
         <f t="shared" si="2"/>
-        <v>6.4655172413793108E-2</v>
+        <v>6.4655172413793094E-2</v>
       </c>
       <c r="E4" s="1">
         <v>1.5</v>
@@ -524,7 +524,7 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="D5" s="2">
         <f t="shared" si="2"/>
-        <v>0.12931034482758622</v>
+        <v>0.12931034482758619</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -547,7 +547,7 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
@@ -593,7 +593,7 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="D11" s="2">
         <f t="shared" si="2"/>
-        <v>1.2931034482758621E-2</v>
+        <v>1.2931034482758617E-2</v>
       </c>
       <c r="E11" s="1">
         <v>0.3</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
@@ -708,7 +708,7 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="D19" s="2">
         <f t="shared" si="2"/>
-        <v>6.4655172413793108E-2</v>
+        <v>6.4655172413793094E-2</v>
       </c>
       <c r="E19" s="1">
         <v>1.5</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
@@ -877,7 +877,7 @@
       </c>
       <c r="D20" s="2">
         <f t="shared" si="2"/>
-        <v>0.12931034482758622</v>
+        <v>0.12931034482758619</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
@@ -984,7 +984,7 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D26" s="2">
         <f t="shared" si="2"/>
-        <v>1.2931034482758621E-2</v>
+        <v>1.2931034482758617E-2</v>
       </c>
       <c r="E26" s="1">
         <v>0.3</v>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="1"/>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
